--- a/legisq-admin/static/dataset/mps.xlsx
+++ b/legisq-admin/static/dataset/mps.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>mp_id</t>
   </si>
@@ -55,7 +55,7 @@
     <t>17-lok sabha</t>
   </si>
   <si>
-    <t>alen tessa</t>
+    <t>Repeat Check</t>
   </si>
   <si>
     <t>bihar</t>
@@ -65,6 +65,27 @@
   </si>
   <si>
     <t>16-Lok Sabha</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Uttar Pradesh</t>
+  </si>
+  <si>
+    <t>ralli</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>Suresh incomplete</t>
+  </si>
+  <si>
+    <t>Kerala</t>
+  </si>
+  <si>
+    <t>Thrissur</t>
   </si>
 </sst>
 </file>
@@ -415,6 +436,58 @@
         <v>17</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>102.0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="1">
+        <v>110.0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>17.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>103.0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="1">
+        <v>-3.0</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
